--- a/skycultures/translations_chinese_star_names.xlsx
+++ b/skycultures/translations_chinese_star_names.xlsx
@@ -38616,39 +38616,6 @@
   </si>
   <si>
     <r>
-      <t>Shu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-      </rPr>
-      <t>ǐ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> We</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-      </rPr>
-      <t>ǐ</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>Xi</t>
     </r>
     <r>
@@ -39499,6 +39466,30 @@
   </si>
   <si>
     <t>Accumulated Water (South)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Shu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>ǐ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Wěi</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -40043,7 +40034,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>6050</v>
+        <v>6049</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1880</v>
@@ -40052,7 +40043,7 @@
         <v>1881</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>4586</v>
@@ -41578,16 +41569,16 @@
         <v>4635</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>6036</v>
+        <v>6035</v>
       </c>
       <c r="H39" s="17" t="s">
+        <v>6141</v>
+      </c>
+      <c r="I39" s="6" t="s">
         <v>6142</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="J39" s="7" t="s">
         <v>6143</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>6144</v>
       </c>
       <c r="K39" s="20" t="s">
         <v>3900</v>
@@ -42544,43 +42535,43 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
+        <v>6050</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>6060</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>6051</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>6061</v>
-      </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="1" t="s">
+        <v>6051</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>6052</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>6052</v>
-      </c>
-      <c r="E63" s="5" t="s">
+      <c r="F63" s="5" t="s">
         <v>6053</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="G63" s="16" t="s">
+        <v>6051</v>
+      </c>
+      <c r="H63" s="16" t="s">
         <v>6054</v>
       </c>
-      <c r="G63" s="16" t="s">
-        <v>6052</v>
-      </c>
-      <c r="H63" s="16" t="s">
+      <c r="I63" s="7" t="s">
         <v>6055</v>
       </c>
-      <c r="I63" s="7" t="s">
+      <c r="J63" s="7" t="s">
         <v>6056</v>
       </c>
-      <c r="J63" s="7" t="s">
+      <c r="K63" s="20" t="s">
         <v>6057</v>
       </c>
-      <c r="K63" s="20" t="s">
+      <c r="L63" s="8" t="s">
         <v>6058</v>
       </c>
-      <c r="L63" s="8" t="s">
+      <c r="M63" s="7" t="s">
         <v>6059</v>
-      </c>
-      <c r="M63" s="7" t="s">
-        <v>6060</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="19" x14ac:dyDescent="0.65">
@@ -42647,7 +42638,7 @@
         <v>208</v>
       </c>
       <c r="H65" s="16" t="s">
-        <v>6033</v>
+        <v>6032</v>
       </c>
       <c r="I65" s="7" t="s">
         <v>2758</v>
@@ -43162,7 +43153,7 @@
         <v>238</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>6074</v>
+        <v>6073</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>239</v>
@@ -43408,7 +43399,7 @@
         <v>258</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>6073</v>
+        <v>6072</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>259</v>
@@ -43979,43 +43970,43 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
+        <v>6062</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>6061</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>6063</v>
       </c>
-      <c r="B98" s="5" t="s">
-        <v>6062</v>
-      </c>
-      <c r="C98" s="1" t="s">
+      <c r="D98" s="1" t="s">
+        <v>6063</v>
+      </c>
+      <c r="E98" s="5" t="s">
         <v>6064</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>6064</v>
-      </c>
-      <c r="E98" s="5" t="s">
+      <c r="F98" s="5" t="s">
         <v>6065</v>
       </c>
-      <c r="F98" s="5" t="s">
+      <c r="G98" s="16" t="s">
+        <v>6063</v>
+      </c>
+      <c r="H98" s="16" t="s">
         <v>6066</v>
       </c>
-      <c r="G98" s="16" t="s">
-        <v>6064</v>
-      </c>
-      <c r="H98" s="16" t="s">
+      <c r="I98" s="7" t="s">
         <v>6067</v>
       </c>
-      <c r="I98" s="7" t="s">
+      <c r="J98" s="7" t="s">
         <v>6068</v>
       </c>
-      <c r="J98" s="7" t="s">
+      <c r="K98" s="20" t="s">
         <v>6069</v>
       </c>
-      <c r="K98" s="20" t="s">
+      <c r="L98" s="8" t="s">
         <v>6070</v>
       </c>
-      <c r="L98" s="8" t="s">
+      <c r="M98" s="7" t="s">
         <v>6071</v>
-      </c>
-      <c r="M98" s="7" t="s">
-        <v>6072</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="19" x14ac:dyDescent="0.65">
@@ -45066,7 +45057,7 @@
         <v>409</v>
       </c>
       <c r="H124" s="16" t="s">
-        <v>6034</v>
+        <v>6033</v>
       </c>
       <c r="I124" s="7" t="s">
         <v>3776</v>
@@ -45619,7 +45610,7 @@
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
-        <v>6075</v>
+        <v>6074</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>1804</v>
@@ -45660,7 +45651,7 @@
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
-        <v>6076</v>
+        <v>6075</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>451</v>
@@ -45701,7 +45692,7 @@
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
-        <v>6075</v>
+        <v>6074</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>454</v>
@@ -45742,7 +45733,7 @@
     </row>
     <row r="141" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A141" s="4" t="s">
-        <v>6077</v>
+        <v>6076</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>442</v>
@@ -45783,7 +45774,7 @@
     </row>
     <row r="142" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A142" s="4" t="s">
-        <v>6078</v>
+        <v>6077</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>444</v>
@@ -45824,7 +45815,7 @@
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
-        <v>6079</v>
+        <v>6078</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>446</v>
@@ -46334,7 +46325,7 @@
         <v>1511</v>
       </c>
       <c r="G155" s="16" t="s">
-        <v>6037</v>
+        <v>6036</v>
       </c>
       <c r="H155" s="16" t="s">
         <v>2947</v>
@@ -46644,7 +46635,7 @@
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
-        <v>6149</v>
+        <v>6148</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>1806</v>
@@ -46685,7 +46676,7 @@
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
-        <v>6150</v>
+        <v>6149</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>1741</v>
@@ -46726,7 +46717,7 @@
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
-        <v>6080</v>
+        <v>6079</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>1738</v>
@@ -46767,7 +46758,7 @@
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
-        <v>6081</v>
+        <v>6080</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>513</v>
@@ -46808,7 +46799,7 @@
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
-        <v>6082</v>
+        <v>6081</v>
       </c>
       <c r="B167" s="9" t="s">
         <v>513</v>
@@ -46849,7 +46840,7 @@
     </row>
     <row r="168" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A168" s="4" t="s">
-        <v>6083</v>
+        <v>6082</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>1739</v>
@@ -46972,7 +46963,7 @@
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
-        <v>6151</v>
+        <v>6150</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>534</v>
@@ -47013,7 +47004,7 @@
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
-        <v>6152</v>
+        <v>6151</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>527</v>
@@ -47054,7 +47045,7 @@
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
-        <v>6152</v>
+        <v>6151</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>531</v>
@@ -47669,7 +47660,7 @@
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
-        <v>6153</v>
+        <v>6152</v>
       </c>
       <c r="B188" s="5" t="s">
         <v>576</v>
@@ -47710,7 +47701,7 @@
     </row>
     <row r="189" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A189" s="4" t="s">
-        <v>6154</v>
+        <v>6153</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>581</v>
@@ -47751,7 +47742,7 @@
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
-        <v>6155</v>
+        <v>6154</v>
       </c>
       <c r="B190" s="5" t="s">
         <v>1799</v>
@@ -47792,7 +47783,7 @@
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
-        <v>6156</v>
+        <v>6155</v>
       </c>
       <c r="B191" s="5" t="s">
         <v>587</v>
@@ -47833,7 +47824,7 @@
     </row>
     <row r="192" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A192" s="4" t="s">
-        <v>6156</v>
+        <v>6155</v>
       </c>
       <c r="B192" s="5" t="s">
         <v>592</v>
@@ -47874,16 +47865,16 @@
     </row>
     <row r="193" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A193" s="4" t="s">
-        <v>6157</v>
+        <v>6156</v>
       </c>
       <c r="B193" s="5" t="s">
         <v>571</v>
       </c>
       <c r="C193" s="1" t="s">
+        <v>6006</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>6007</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>6008</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>572</v>
@@ -47915,7 +47906,7 @@
     </row>
     <row r="194" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A194" s="4" t="s">
-        <v>6158</v>
+        <v>6157</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>573</v>
@@ -48612,7 +48603,7 @@
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
-        <v>6084</v>
+        <v>6083</v>
       </c>
       <c r="B211" s="5" t="s">
         <v>639</v>
@@ -48653,7 +48644,7 @@
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
-        <v>6085</v>
+        <v>6084</v>
       </c>
       <c r="B212" s="5" t="s">
         <v>1810</v>
@@ -48694,7 +48685,7 @@
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
-        <v>6086</v>
+        <v>6085</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>634</v>
@@ -48735,7 +48726,7 @@
     </row>
     <row r="214" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A214" s="4" t="s">
-        <v>6086</v>
+        <v>6085</v>
       </c>
       <c r="B214" s="5" t="s">
         <v>637</v>
@@ -49002,7 +48993,7 @@
         <v>3101</v>
       </c>
       <c r="H220" s="16" t="s">
-        <v>6035</v>
+        <v>6034</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>3102</v>
@@ -49555,7 +49546,7 @@
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
-        <v>6101</v>
+        <v>6100</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>753</v>
@@ -49596,7 +49587,7 @@
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
-        <v>6102</v>
+        <v>6101</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>710</v>
@@ -49637,7 +49628,7 @@
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
-        <v>6103</v>
+        <v>6102</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>714</v>
@@ -49678,7 +49669,7 @@
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
-        <v>6104</v>
+        <v>6103</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>729</v>
@@ -49719,7 +49710,7 @@
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
-        <v>6113</v>
+        <v>6112</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>741</v>
@@ -49760,7 +49751,7 @@
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
-        <v>6114</v>
+        <v>6113</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>745</v>
@@ -49801,7 +49792,7 @@
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
-        <v>6105</v>
+        <v>6104</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>749</v>
@@ -49842,7 +49833,7 @@
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
-        <v>6110</v>
+        <v>6109</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>737</v>
@@ -49883,7 +49874,7 @@
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
-        <v>6111</v>
+        <v>6110</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>726</v>
@@ -49924,7 +49915,7 @@
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
-        <v>6115</v>
+        <v>6114</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>733</v>
@@ -49965,7 +49956,7 @@
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
-        <v>6116</v>
+        <v>6115</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>718</v>
@@ -50006,7 +49997,7 @@
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
-        <v>6106</v>
+        <v>6105</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>706</v>
@@ -50047,7 +50038,7 @@
     </row>
     <row r="246" spans="1:13" s="7" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="22" t="s">
-        <v>6117</v>
+        <v>6116</v>
       </c>
       <c r="B246" s="7" t="s">
         <v>722</v>
@@ -50088,7 +50079,7 @@
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
-        <v>6102</v>
+        <v>6101</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>759</v>
@@ -50129,7 +50120,7 @@
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
-        <v>6103</v>
+        <v>6102</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>761</v>
@@ -50170,7 +50161,7 @@
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
-        <v>6104</v>
+        <v>6103</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>771</v>
@@ -50211,7 +50202,7 @@
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
-        <v>6113</v>
+        <v>6112</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>777</v>
@@ -50252,7 +50243,7 @@
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
-        <v>6114</v>
+        <v>6113</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>779</v>
@@ -50293,7 +50284,7 @@
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
-        <v>6105</v>
+        <v>6104</v>
       </c>
       <c r="B252" s="5" t="s">
         <v>782</v>
@@ -50334,7 +50325,7 @@
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
-        <v>6110</v>
+        <v>6109</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>775</v>
@@ -50375,7 +50366,7 @@
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
-        <v>6111</v>
+        <v>6110</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>769</v>
@@ -50416,7 +50407,7 @@
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
-        <v>6115</v>
+        <v>6114</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>773</v>
@@ -50457,7 +50448,7 @@
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
-        <v>6116</v>
+        <v>6115</v>
       </c>
       <c r="B256" s="5" t="s">
         <v>763</v>
@@ -50498,7 +50489,7 @@
     </row>
     <row r="257" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
-        <v>6106</v>
+        <v>6105</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>756</v>
@@ -50539,7 +50530,7 @@
     </row>
     <row r="258" spans="1:13" s="7" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="22" t="s">
-        <v>6117</v>
+        <v>6116</v>
       </c>
       <c r="B258" s="7" t="s">
         <v>766</v>
@@ -50580,7 +50571,7 @@
     </row>
     <row r="259" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
-        <v>6118</v>
+        <v>6117</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>1815</v>
@@ -50621,7 +50612,7 @@
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
-        <v>6107</v>
+        <v>6106</v>
       </c>
       <c r="B260" s="5" t="s">
         <v>690</v>
@@ -50662,7 +50653,7 @@
     </row>
     <row r="261" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
-        <v>6108</v>
+        <v>6107</v>
       </c>
       <c r="B261" s="5" t="s">
         <v>694</v>
@@ -50703,7 +50694,7 @@
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
-        <v>6109</v>
+        <v>6108</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>697</v>
@@ -50744,7 +50735,7 @@
     </row>
     <row r="263" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A263" s="4" t="s">
-        <v>6112</v>
+        <v>6111</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>700</v>
@@ -50785,7 +50776,7 @@
     </row>
     <row r="264" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A264" s="4" t="s">
-        <v>6119</v>
+        <v>6118</v>
       </c>
       <c r="B264" s="5" t="s">
         <v>703</v>
@@ -51441,7 +51432,7 @@
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
-        <v>6120</v>
+        <v>6119</v>
       </c>
       <c r="B280" s="5" t="s">
         <v>1819</v>
@@ -51482,7 +51473,7 @@
     </row>
     <row r="281" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A281" s="4" t="s">
-        <v>6120</v>
+        <v>6119</v>
       </c>
       <c r="B281" s="5" t="s">
         <v>838</v>
@@ -51523,7 +51514,7 @@
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
-        <v>6121</v>
+        <v>6120</v>
       </c>
       <c r="B282" s="5" t="s">
         <v>845</v>
@@ -51564,7 +51555,7 @@
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
-        <v>6121</v>
+        <v>6120</v>
       </c>
       <c r="B283" s="5" t="s">
         <v>847</v>
@@ -51687,7 +51678,7 @@
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
-        <v>6122</v>
+        <v>6121</v>
       </c>
       <c r="B286" s="5" t="s">
         <v>1743</v>
@@ -51728,7 +51719,7 @@
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
-        <v>6123</v>
+        <v>6122</v>
       </c>
       <c r="B287" s="5" t="s">
         <v>852</v>
@@ -51769,7 +51760,7 @@
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
-        <v>6123</v>
+        <v>6122</v>
       </c>
       <c r="B288" s="5" t="s">
         <v>856</v>
@@ -51810,7 +51801,7 @@
     </row>
     <row r="289" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A289" s="4" t="s">
-        <v>6123</v>
+        <v>6122</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>859</v>
@@ -51851,7 +51842,7 @@
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
-        <v>6124</v>
+        <v>6123</v>
       </c>
       <c r="B290" s="5" t="s">
         <v>1798</v>
@@ -51892,7 +51883,7 @@
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
-        <v>6125</v>
+        <v>6124</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>830</v>
@@ -51933,7 +51924,7 @@
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
-        <v>6126</v>
+        <v>6125</v>
       </c>
       <c r="B292" s="5" t="s">
         <v>834</v>
@@ -52343,7 +52334,7 @@
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
-        <v>6127</v>
+        <v>6126</v>
       </c>
       <c r="B302" s="5" t="s">
         <v>1744</v>
@@ -52384,7 +52375,7 @@
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
-        <v>6128</v>
+        <v>6127</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>913</v>
@@ -52443,7 +52434,7 @@
         <v>1590</v>
       </c>
       <c r="G304" s="16" t="s">
-        <v>6038</v>
+        <v>6037</v>
       </c>
       <c r="H304" s="16" t="s">
         <v>3032</v>
@@ -52548,7 +52539,7 @@
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
-        <v>6129</v>
+        <v>6128</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>1822</v>
@@ -52589,7 +52580,7 @@
     </row>
     <row r="308" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A308" s="4" t="s">
-        <v>6130</v>
+        <v>6129</v>
       </c>
       <c r="B308" s="5" t="s">
         <v>1745</v>
@@ -52630,7 +52621,7 @@
     </row>
     <row r="309" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A309" s="4" t="s">
-        <v>6131</v>
+        <v>6130</v>
       </c>
       <c r="B309" s="5" t="s">
         <v>890</v>
@@ -52671,7 +52662,7 @@
     </row>
     <row r="310" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A310" s="4" t="s">
-        <v>6132</v>
+        <v>6131</v>
       </c>
       <c r="B310" s="5" t="s">
         <v>907</v>
@@ -52689,7 +52680,7 @@
         <v>5015</v>
       </c>
       <c r="G310" s="16" t="s">
-        <v>6039</v>
+        <v>6038</v>
       </c>
       <c r="H310" s="16" t="s">
         <v>3286</v>
@@ -52712,7 +52703,7 @@
     </row>
     <row r="311" spans="1:13" ht="19" x14ac:dyDescent="0.65">
       <c r="A311" s="4" t="s">
-        <v>6132</v>
+        <v>6131</v>
       </c>
       <c r="B311" s="5" t="s">
         <v>907</v>
@@ -53796,7 +53787,7 @@
         <v>1554</v>
       </c>
       <c r="G337" s="16" t="s">
-        <v>6040</v>
+        <v>6039</v>
       </c>
       <c r="H337" s="16" t="s">
         <v>3347</v>
@@ -53983,7 +53974,7 @@
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A342" s="4" t="s">
-        <v>6147</v>
+        <v>6146</v>
       </c>
       <c r="B342" s="5" t="s">
         <v>998</v>
@@ -54024,7 +54015,7 @@
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A343" s="4" t="s">
-        <v>6148</v>
+        <v>6147</v>
       </c>
       <c r="B343" s="5" t="s">
         <v>995</v>
@@ -54042,7 +54033,7 @@
         <v>1556</v>
       </c>
       <c r="G343" s="16" t="s">
-        <v>6041</v>
+        <v>6040</v>
       </c>
       <c r="H343" s="16" t="s">
         <v>3361</v>
@@ -54639,7 +54630,7 @@
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
-        <v>6133</v>
+        <v>6132</v>
       </c>
       <c r="B358" s="5" t="s">
         <v>1045</v>
@@ -54680,7 +54671,7 @@
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
-        <v>6134</v>
+        <v>6133</v>
       </c>
       <c r="B359" s="5" t="s">
         <v>1048</v>
@@ -54721,7 +54712,7 @@
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
-        <v>6135</v>
+        <v>6134</v>
       </c>
       <c r="B360" s="5" t="s">
         <v>1036</v>
@@ -54762,7 +54753,7 @@
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
-        <v>6136</v>
+        <v>6135</v>
       </c>
       <c r="B361" s="5" t="s">
         <v>1038</v>
@@ -54803,7 +54794,7 @@
     </row>
     <row r="362" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
-        <v>6137</v>
+        <v>6136</v>
       </c>
       <c r="B362" s="5" t="s">
         <v>1746</v>
@@ -55436,7 +55427,7 @@
         <v>4620</v>
       </c>
       <c r="G377" s="16" t="s">
-        <v>6042</v>
+        <v>6041</v>
       </c>
       <c r="H377" s="16" t="s">
         <v>3029</v>
@@ -55600,7 +55591,7 @@
         <v>1652</v>
       </c>
       <c r="G381" s="16" t="s">
-        <v>6043</v>
+        <v>6042</v>
       </c>
       <c r="H381" s="16" t="s">
         <v>3438</v>
@@ -55787,7 +55778,7 @@
     </row>
     <row r="386" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
-        <v>6138</v>
+        <v>6137</v>
       </c>
       <c r="B386" s="5" t="s">
         <v>1118</v>
@@ -55828,7 +55819,7 @@
     </row>
     <row r="387" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
-        <v>6138</v>
+        <v>6137</v>
       </c>
       <c r="B387" s="5" t="s">
         <v>1118</v>
@@ -55869,7 +55860,7 @@
     </row>
     <row r="388" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
-        <v>6139</v>
+        <v>6138</v>
       </c>
       <c r="B388" s="5" t="s">
         <v>1115</v>
@@ -56944,7 +56935,7 @@
         <v>1852</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>6009</v>
+        <v>6008</v>
       </c>
       <c r="E414" s="5" t="s">
         <v>5162</v>
@@ -57020,7 +57011,7 @@
         <v>2217</v>
       </c>
       <c r="B416" s="5" t="s">
-        <v>6159</v>
+        <v>6158</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>1186</v>
@@ -57061,7 +57052,7 @@
         <v>2217</v>
       </c>
       <c r="B417" s="5" t="s">
-        <v>6160</v>
+        <v>6159</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>1854</v>
@@ -57240,7 +57231,7 @@
         <v>1575</v>
       </c>
       <c r="G421" s="16" t="s">
-        <v>6044</v>
+        <v>6043</v>
       </c>
       <c r="H421" s="16" t="s">
         <v>3514</v>
@@ -58060,7 +58051,7 @@
         <v>5203</v>
       </c>
       <c r="G441" s="16" t="s">
-        <v>6045</v>
+        <v>6044</v>
       </c>
       <c r="H441" s="16" t="s">
         <v>3549</v>
@@ -58165,7 +58156,7 @@
     </row>
     <row r="444" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
-        <v>6145</v>
+        <v>6144</v>
       </c>
       <c r="B444" s="5" t="s">
         <v>1259</v>
@@ -58206,7 +58197,7 @@
     </row>
     <row r="445" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
-        <v>6146</v>
+        <v>6145</v>
       </c>
       <c r="B445" s="5" t="s">
         <v>1256</v>
@@ -58953,7 +58944,7 @@
         <v>1303</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>6010</v>
+        <v>6009</v>
       </c>
       <c r="E463" s="5" t="s">
         <v>1305</v>
@@ -60145,7 +60136,7 @@
         <v>1718</v>
       </c>
       <c r="E492" s="10" t="s">
-        <v>6004</v>
+        <v>6160</v>
       </c>
       <c r="F492" s="5" t="s">
         <v>1790</v>
@@ -60432,7 +60423,7 @@
         <v>1732</v>
       </c>
       <c r="E499" s="10" t="s">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="F499" s="5" t="s">
         <v>5273</v>
@@ -60573,7 +60564,7 @@
         <v>5279</v>
       </c>
       <c r="K502" s="20" t="s">
-        <v>6049</v>
+        <v>6048</v>
       </c>
       <c r="L502" s="8" t="s">
         <v>5921</v>
@@ -60631,7 +60622,7 @@
         <v>2441</v>
       </c>
       <c r="C505" s="15" t="s">
-        <v>6029</v>
+        <v>6028</v>
       </c>
       <c r="D505" s="1" t="s">
         <v>2406</v>
@@ -60657,7 +60648,7 @@
         <v>2442</v>
       </c>
       <c r="C506" s="15" t="s">
-        <v>6030</v>
+        <v>6029</v>
       </c>
       <c r="D506" s="1" t="s">
         <v>2286</v>
@@ -60683,7 +60674,7 @@
         <v>2443</v>
       </c>
       <c r="C507" s="15" t="s">
-        <v>6031</v>
+        <v>6030</v>
       </c>
       <c r="D507" s="1" t="s">
         <v>2287</v>
@@ -60761,7 +60752,7 @@
         <v>2446</v>
       </c>
       <c r="C510" s="15" t="s">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="D510" s="1" t="s">
         <v>2292</v>
@@ -61252,7 +61243,7 @@
         <v>2370</v>
       </c>
       <c r="B529" s="12" t="s">
-        <v>6140</v>
+        <v>6139</v>
       </c>
       <c r="C529" s="1" t="s">
         <v>2312</v>
@@ -61278,7 +61269,7 @@
         <v>2371</v>
       </c>
       <c r="B530" s="12" t="s">
-        <v>6141</v>
+        <v>6140</v>
       </c>
       <c r="C530" s="1" t="s">
         <v>2313</v>
@@ -61746,25 +61737,25 @@
         <v>2389</v>
       </c>
       <c r="B548" s="12" t="s">
+        <v>6093</v>
+      </c>
+      <c r="C548" s="1" t="s">
         <v>6094</v>
       </c>
-      <c r="C548" s="1" t="s">
+      <c r="D548" s="1" t="s">
         <v>6095</v>
       </c>
-      <c r="D548" s="1" t="s">
+      <c r="G548" s="17" t="s">
         <v>6096</v>
       </c>
-      <c r="G548" s="17" t="s">
+      <c r="H548" s="17" t="s">
         <v>6097</v>
       </c>
-      <c r="H548" s="17" t="s">
+      <c r="I548" s="6" t="s">
         <v>6098</v>
       </c>
-      <c r="I548" s="6" t="s">
+      <c r="J548" s="6" t="s">
         <v>6099</v>
-      </c>
-      <c r="J548" s="6" t="s">
-        <v>6100</v>
       </c>
     </row>
     <row r="549" spans="1:10" x14ac:dyDescent="0.3">
@@ -61798,25 +61789,25 @@
         <v>2391</v>
       </c>
       <c r="B550" s="12" t="s">
-        <v>6092</v>
+        <v>6091</v>
       </c>
       <c r="C550" s="1" t="s">
+        <v>6086</v>
+      </c>
+      <c r="D550" s="1" t="s">
+        <v>6088</v>
+      </c>
+      <c r="G550" s="17" t="s">
+        <v>6086</v>
+      </c>
+      <c r="H550" s="17" t="s">
         <v>6087</v>
       </c>
-      <c r="D550" s="1" t="s">
+      <c r="I550" s="6" t="s">
         <v>6089</v>
       </c>
-      <c r="G550" s="17" t="s">
-        <v>6087</v>
-      </c>
-      <c r="H550" s="17" t="s">
-        <v>6088</v>
-      </c>
-      <c r="I550" s="6" t="s">
+      <c r="J550" s="6" t="s">
         <v>6090</v>
-      </c>
-      <c r="J550" s="6" t="s">
-        <v>6091</v>
       </c>
     </row>
     <row r="551" spans="1:10" x14ac:dyDescent="0.3">
@@ -61989,7 +61980,7 @@
         <v>2435</v>
       </c>
       <c r="G557" s="17" t="s">
-        <v>6048</v>
+        <v>6047</v>
       </c>
       <c r="H557" s="17" t="s">
         <v>2564</v>
@@ -62185,7 +62176,7 @@
     </row>
     <row r="565" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A565" s="4" t="s">
-        <v>6093</v>
+        <v>6092</v>
       </c>
       <c r="B565" s="12" t="s">
         <v>2475</v>
@@ -62467,7 +62458,7 @@
         <v>2012</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>2027</v>
@@ -63037,7 +63028,7 @@
         <v>2079</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>6012</v>
+        <v>6011</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>2034</v>
@@ -63075,7 +63066,7 @@
         <v>2080</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>6013</v>
+        <v>6012</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>2035</v>
@@ -63113,7 +63104,7 @@
         <v>2081</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>6014</v>
+        <v>6013</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>2036</v>
@@ -63151,7 +63142,7 @@
         <v>2082</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>6015</v>
+        <v>6014</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>2037</v>
@@ -63239,7 +63230,7 @@
         <v>2063</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>6046</v>
+        <v>6045</v>
       </c>
       <c r="H27" s="16" t="s">
         <v>3257</v>
@@ -63277,7 +63268,7 @@
         <v>1521</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>6047</v>
+        <v>6046</v>
       </c>
       <c r="H28" s="16" t="s">
         <v>2880</v>
@@ -63496,7 +63487,7 @@
         <v>2052</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>6016</v>
+        <v>6015</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>2007</v>
@@ -63531,10 +63522,10 @@
         <v>2076</v>
       </c>
       <c r="C35" s="15" t="s">
+        <v>6016</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>6017</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>6018</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>2003</v>
@@ -63569,10 +63560,10 @@
         <v>2077</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>6019</v>
+        <v>6018</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>6019</v>
+        <v>6018</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>2004</v>
@@ -63610,7 +63601,7 @@
         <v>2056</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>6020</v>
+        <v>6019</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>2006</v>
@@ -63683,10 +63674,10 @@
         <v>2072</v>
       </c>
       <c r="C39" s="15" t="s">
+        <v>6020</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>6021</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>6022</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>2005</v>
@@ -63721,10 +63712,10 @@
         <v>2073</v>
       </c>
       <c r="C40" s="15" t="s">
+        <v>6022</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>6023</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>6024</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>2004</v>
@@ -63759,10 +63750,10 @@
         <v>2074</v>
       </c>
       <c r="C41" s="15" t="s">
+        <v>6024</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>6025</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>6026</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>2003</v>
@@ -63797,10 +63788,10 @@
         <v>2071</v>
       </c>
       <c r="C42" s="15" t="s">
+        <v>6026</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>6027</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>6028</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>2002</v>
